--- a/نتایج/0110AP01.xlsx
+++ b/نتایج/0110AP01.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RCM\نتایج\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haddadnia\Documents\GitHub\RCM_data_concatinating\نتایج\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="294">
   <si>
     <t>AssetNumber</t>
   </si>
@@ -968,16 +968,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -1019,6 +1009,16 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1033,7 +1033,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L168" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L168" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:L168"/>
   <tableColumns count="12">
     <tableColumn id="1" name="AssetNumber"/>
@@ -2021,7 +2021,7 @@
         <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -2600,6 +2600,9 @@
       <c r="D62" t="s">
         <v>78</v>
       </c>
+      <c r="E62" t="s">
+        <v>126</v>
+      </c>
       <c r="F62">
         <v>10</v>
       </c>
@@ -2617,6 +2620,9 @@
       <c r="D63" t="s">
         <v>79</v>
       </c>
+      <c r="E63" t="s">
+        <v>126</v>
+      </c>
       <c r="F63">
         <v>10</v>
       </c>
@@ -2634,6 +2640,9 @@
       <c r="D64" t="s">
         <v>79</v>
       </c>
+      <c r="E64" t="s">
+        <v>126</v>
+      </c>
       <c r="F64">
         <v>10</v>
       </c>
@@ -2651,6 +2660,9 @@
       <c r="D65" t="s">
         <v>80</v>
       </c>
+      <c r="E65" t="s">
+        <v>126</v>
+      </c>
       <c r="F65">
         <v>10</v>
       </c>
@@ -3768,6 +3780,9 @@
       <c r="D121" t="s">
         <v>95</v>
       </c>
+      <c r="E121" t="s">
+        <v>126</v>
+      </c>
       <c r="F121">
         <v>10</v>
       </c>
@@ -3785,6 +3800,9 @@
       <c r="D122" t="s">
         <v>95</v>
       </c>
+      <c r="E122" t="s">
+        <v>126</v>
+      </c>
       <c r="F122">
         <v>10</v>
       </c>
@@ -3802,6 +3820,9 @@
       <c r="D123" t="s">
         <v>95</v>
       </c>
+      <c r="E123" t="s">
+        <v>126</v>
+      </c>
       <c r="F123">
         <v>10</v>
       </c>
@@ -3819,6 +3840,9 @@
       <c r="D124" t="s">
         <v>95</v>
       </c>
+      <c r="E124" t="s">
+        <v>126</v>
+      </c>
       <c r="F124">
         <v>10</v>
       </c>
@@ -3836,6 +3860,9 @@
       <c r="D125" t="s">
         <v>70</v>
       </c>
+      <c r="E125" t="s">
+        <v>126</v>
+      </c>
       <c r="F125">
         <v>10</v>
       </c>
@@ -3853,6 +3880,9 @@
       <c r="D126" t="s">
         <v>70</v>
       </c>
+      <c r="E126" t="s">
+        <v>126</v>
+      </c>
       <c r="F126">
         <v>10</v>
       </c>
@@ -3870,6 +3900,9 @@
       <c r="D127" t="s">
         <v>96</v>
       </c>
+      <c r="E127" t="s">
+        <v>126</v>
+      </c>
       <c r="F127">
         <v>10</v>
       </c>
@@ -4702,7 +4735,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
